--- a/GRAMMAR/3_22_07.xlsx
+++ b/GRAMMAR/3_22_07.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\GRAMMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBD672D-5A73-4DF0-88ED-11A835B75B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577D881D-272B-4400-94D2-A9195BBC98A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18255" yWindow="1335" windowWidth="27840" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Fre</t>
   </si>
@@ -126,9 +126,6 @@
     <t>だけ</t>
   </si>
   <si>
-    <t>只，仅；尽可能…(最高程度)</t>
-  </si>
-  <si>
     <t>わりに</t>
   </si>
   <si>
@@ -203,13 +200,77 @@
   <si>
     <t>といえる-&gt;可以说...
 といえば-&gt;说到…</t>
+  </si>
+  <si>
+    <t>寝坊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>睡懒觉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>とはいえ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虽说…但是…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>てでも</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>就算…也要…(不惜一切代价做某事)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只，仅；尽可能…(最高程度)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>これから</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>接下来…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>休む</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请假；缺勤;休息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>とのことだ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传闻…；据说…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>みたいだ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)以外在事物(规定、说明)为根据的推测(2)比喻(3)示例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「はず」根据自己的常识、经验的推测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,13 +279,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -266,11 +337,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -573,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -601,279 +673,406 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A5">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>1</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A7">
-        <v>0</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="A7" s="2">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E7" t="s">
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A8">
-        <v>0</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="A8" s="2">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E8" t="s">
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9">
-        <v>0</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="A9" s="2">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A10">
-        <v>0</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="A10" s="2">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A11">
-        <v>0</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="A11" s="2">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A12">
-        <v>0</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="A12" s="2">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13" s="2">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A13">
-        <v>0</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14" s="2">
+        <v>1</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A14">
+      <c r="C14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15" s="2">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" s="2">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A17" s="2">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A18" s="2">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" s="2">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A20" s="2">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A21" s="2">
         <v>1</v>
       </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A15">
-        <v>0</v>
-      </c>
-      <c r="B15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A16">
-        <v>0</v>
-      </c>
-      <c r="B16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17">
-        <v>0</v>
-      </c>
-      <c r="B17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18">
-        <v>0</v>
-      </c>
-      <c r="B18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19">
-        <v>0</v>
-      </c>
-      <c r="B19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20">
-        <v>0</v>
-      </c>
-      <c r="B20" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B21" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21">
-        <v>1</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A22" s="2">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22">
-        <v>0</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A23" s="2">
+        <v>0</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23">
-        <v>0</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" s="2"/>
+      <c r="E23" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E23" t="s">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A24" s="2">
+        <v>2</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="C24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A25" s="2">
+        <v>2</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A26" s="2">
+        <v>2</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A27" s="2">
+        <v>2</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A28" s="2">
+        <v>2</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A29" s="2">
+        <v>2</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A30" s="2">
+        <v>2</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -884,7 +1083,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -894,7 +1093,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/GRAMMAR/3_22_07.xlsx
+++ b/GRAMMAR/3_22_07.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\GRAMMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCEF8F1B-0C79-4D7D-9708-B3FEFCA788A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBD672D-5A73-4DF0-88ED-11A835B75B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10275" yWindow="690" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Fre</t>
   </si>
@@ -39,24 +39,6 @@
     <t>备注</t>
   </si>
   <si>
-    <t>とのことだ</t>
-  </si>
-  <si>
-    <t>传闻…；据说…</t>
-  </si>
-  <si>
-    <t>これから</t>
-  </si>
-  <si>
-    <t>接下来…</t>
-  </si>
-  <si>
-    <t>てでも</t>
-  </si>
-  <si>
-    <t>就算…也要…(不惜一切代价做某事)</t>
-  </si>
-  <si>
     <t>〜にともなって</t>
   </si>
   <si>
@@ -66,30 +48,6 @@
     <t>～にともない-&gt;伴随着…</t>
   </si>
   <si>
-    <t>请假；缺勤;休息</t>
-  </si>
-  <si>
-    <t>とはいえ</t>
-  </si>
-  <si>
-    <t>虽说…但是…</t>
-  </si>
-  <si>
-    <t>寝坊</t>
-  </si>
-  <si>
-    <t>睡懒觉</t>
-  </si>
-  <si>
-    <t>みたいだ</t>
-  </si>
-  <si>
-    <t>(1)以外在事物(规定、说明)为根据的推测(2)比喻(3)示例</t>
-  </si>
-  <si>
-    <t>「はず」根据自己的常识、经验的推测</t>
-  </si>
-  <si>
     <t>取り組み</t>
   </si>
   <si>
@@ -100,25 +58,6 @@
   </si>
   <si>
     <t>取り上げる-&gt;提出，举出</t>
-  </si>
-  <si>
-    <t>〜にこたえて</t>
-  </si>
-  <si>
-    <t>回应...，响应...</t>
-  </si>
-  <si>
-    <t>话虽如此，尽管说...</t>
-  </si>
-  <si>
-    <t>といえば-&gt;说到...
-だとえば-&gt;比如…</t>
-  </si>
-  <si>
-    <t>ということだ/とのことだ+…+によると</t>
-  </si>
-  <si>
-    <t>据说，听说</t>
   </si>
   <si>
     <t>〜ないでもない</t>
@@ -132,6 +71,70 @@
 Ｖる＋までもない-&gt;没必要</t>
   </si>
   <si>
+    <t>とはいえ</t>
+  </si>
+  <si>
+    <t>话虽如此，尽管说...</t>
+  </si>
+  <si>
+    <t>といえば-&gt;说到...
+だとえば-&gt;比如…</t>
+  </si>
+  <si>
+    <t>〜にこたえて</t>
+  </si>
+  <si>
+    <t>回应...，响应...</t>
+  </si>
+  <si>
+    <t>時間+より</t>
+  </si>
+  <si>
+    <t>从…(开始)</t>
+  </si>
+  <si>
+    <t>というより-&gt;与其说…倒不如…</t>
+  </si>
+  <si>
+    <t>いまにも〜そう</t>
+  </si>
+  <si>
+    <t>眼看就要...似的，马上就...</t>
+  </si>
+  <si>
+    <t>いつのまに-&gt;不知不觉地(已经发生的事)</t>
+  </si>
+  <si>
+    <t>ようやく</t>
+  </si>
+  <si>
+    <t>好不容易，终于</t>
+  </si>
+  <si>
+    <t>そのうち</t>
+  </si>
+  <si>
+    <t>不久，过几天</t>
+  </si>
+  <si>
+    <t>V+てでも</t>
+  </si>
+  <si>
+    <t>即使...也要...，不惜...</t>
+  </si>
+  <si>
+    <t>だけ</t>
+  </si>
+  <si>
+    <t>只，仅；尽可能…(最高程度)</t>
+  </si>
+  <si>
+    <t>わりに</t>
+  </si>
+  <si>
+    <t>与...相比算是...，意外地</t>
+  </si>
+  <si>
     <t>数量詞+も+〜+ば/たら/と</t>
   </si>
   <si>
@@ -141,48 +144,48 @@
     <t>数量词+も：(1)数量之多，程度深 (2)接否定</t>
   </si>
   <si>
+    <t>づらい</t>
+  </si>
+  <si>
+    <t>难以；不便；不容易</t>
+  </si>
+  <si>
+    <t>うち</t>
+  </si>
+  <si>
+    <t>家；我们；期间</t>
+  </si>
+  <si>
+    <t>かねない</t>
+  </si>
+  <si>
+    <t>（有可能会）发生（不好的事）</t>
+  </si>
+  <si>
+    <t>ということだ/とのことだ+…+によると</t>
+  </si>
+  <si>
+    <t>据说，听说</t>
+  </si>
+  <si>
+    <t>〜みたいだ</t>
+  </si>
+  <si>
+    <t>好像......，像......一样</t>
+  </si>
+  <si>
+    <t>〜それほど〜ない</t>
+  </si>
+  <si>
+    <t>没那么......</t>
+  </si>
+  <si>
     <t>だが</t>
   </si>
   <si>
     <t>但是，可是</t>
   </si>
   <si>
-    <t>〜それほど〜ない</t>
-  </si>
-  <si>
-    <t>没那么......</t>
-  </si>
-  <si>
-    <t>わりに</t>
-  </si>
-  <si>
-    <t>与...相比算是...，意外地</t>
-  </si>
-  <si>
-    <t>づらい</t>
-  </si>
-  <si>
-    <t>难以；不便；不容易</t>
-  </si>
-  <si>
-    <t>そのうち</t>
-  </si>
-  <si>
-    <t>不久，过几天</t>
-  </si>
-  <si>
-    <t>かねない</t>
-  </si>
-  <si>
-    <t>（有可能会）发生（不好的事）</t>
-  </si>
-  <si>
-    <t>〜みたいだ</t>
-  </si>
-  <si>
-    <t>好像......，像......一样</t>
-  </si>
-  <si>
     <t>暗証番号</t>
   </si>
   <si>
@@ -190,18 +193,6 @@
   </si>
   <si>
     <t>あんしょうばんごう</t>
-  </si>
-  <si>
-    <t>だけ</t>
-  </si>
-  <si>
-    <t>只，仅；尽可能…(最高程度)</t>
-  </si>
-  <si>
-    <t>V+てでも</t>
-  </si>
-  <si>
-    <t>即使...也要...，不惜...</t>
   </si>
   <si>
     <t>たとえば</t>
@@ -212,40 +203,6 @@
   <si>
     <t>といえる-&gt;可以说...
 といえば-&gt;说到…</t>
-  </si>
-  <si>
-    <t>ようやく</t>
-  </si>
-  <si>
-    <t>好不容易，终于</t>
-  </si>
-  <si>
-    <t>いまにも〜そう</t>
-  </si>
-  <si>
-    <t>眼看就要...似的，马上就...</t>
-  </si>
-  <si>
-    <t>いつのまに-&gt;不知不觉地(已经发生的事)</t>
-  </si>
-  <si>
-    <t>時間+より</t>
-  </si>
-  <si>
-    <t>从…(开始)</t>
-  </si>
-  <si>
-    <t>というより-&gt;与其说…倒不如…</t>
-  </si>
-  <si>
-    <t>うち</t>
-  </si>
-  <si>
-    <t>家；我们；期间</t>
-  </si>
-  <si>
-    <t>休む</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -616,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -645,7 +602,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -653,141 +610,147 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
@@ -795,38 +758,35 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.15">
@@ -834,10 +794,10 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.15">
@@ -845,10 +805,10 @@
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.15">
@@ -856,10 +816,10 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.15">
@@ -867,32 +827,35 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="D22" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
@@ -900,99 +863,13 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24">
-        <v>1</v>
-      </c>
-      <c r="B24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A25">
-        <v>0</v>
-      </c>
-      <c r="B25" t="s">
         <v>57</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E23" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A26">
-        <v>0</v>
-      </c>
-      <c r="B26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" t="s">
-        <v>60</v>
-      </c>
-      <c r="E26" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A27">
-        <v>0</v>
-      </c>
-      <c r="B27" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A28">
-        <v>0</v>
-      </c>
-      <c r="B28" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" t="s">
-        <v>65</v>
-      </c>
-      <c r="E28" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A29">
-        <v>0</v>
-      </c>
-      <c r="B29" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" t="s">
-        <v>68</v>
-      </c>
-      <c r="E29" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A30">
-        <v>0</v>
-      </c>
-      <c r="B30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
